--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654614</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>136654616</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>136654621</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136654622</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136654623</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136654630</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136654636</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>136654631</v>
       </c>
       <c r="B10" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654614</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>136654616</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>136654621</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136654622</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136654623</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136654630</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136654636</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>136654631</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33133-2026 artfynd.xlsx
+++ b/artfynd/A 33133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654638</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654614</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>136654616</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>136654621</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136654622</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136654623</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136654630</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136654636</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>136654631</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
